--- a/lottery_config.xlsx
+++ b/lottery_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV_AREA\lottery_predictor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2BEE82-5C1F-41D6-8596-234B1717E9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C886DA-BD0F-41F9-B797-914A5C05B0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4995" yWindow="2355" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="945" yWindow="75" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTTERY_CONFIGS" sheetId="1" r:id="rId1"/>
@@ -727,7 +727,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="4">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>

--- a/lottery_config.xlsx
+++ b/lottery_config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29916"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV_AREA\lottery_predictor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C886DA-BD0F-41F9-B797-914A5C05B0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F53DA7-6BC2-446C-B39B-DD702EE9289D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="945" yWindow="75" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -727,7 +727,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="4">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>

--- a/lottery_config.xlsx
+++ b/lottery_config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV_AREA\lottery_predictor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F53DA7-6BC2-446C-B39B-DD702EE9289D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5861346A-AF7D-4904-9F8C-B4ACC37CFCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="945" yWindow="75" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -727,7 +727,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="4">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>

--- a/lottery_config.xlsx
+++ b/lottery_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV_AREA\lottery_predictor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5861346A-AF7D-4904-9F8C-B4ACC37CFCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6216C1-07A5-4A03-A2FE-7C5400894EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="75" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1365" yWindow="330" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTTERY_CONFIGS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>lottery_name</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>`</t>
+  </si>
+  <si>
+    <t>confidence_window_count</t>
+  </si>
+  <si>
+    <t>Number of recent windows to use for confidence calculation</t>
   </si>
 </sst>
 </file>
@@ -703,12 +709,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="67.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,7 +733,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>
@@ -746,27 +752,39 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B6" s="4">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/lottery_config.xlsx
+++ b/lottery_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV_AREA\lottery_predictor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6216C1-07A5-4A03-A2FE-7C5400894EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4706F3-0956-4399-A237-27AAA8454280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1365" yWindow="330" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>lottery_name</t>
   </si>
@@ -159,13 +159,16 @@
   </si>
   <si>
     <t>Number of recent windows to use for confidence calculation</t>
+  </si>
+  <si>
+    <t>max_draws_to_use</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +187,18 @@
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -212,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -226,6 +241,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,7 +583,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -709,7 +734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
@@ -729,57 +754,66 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="4">
-        <v>100</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
+      <c r="A2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="4">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B7" s="4">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>42</v>
       </c>
     </row>

--- a/lottery_config.xlsx
+++ b/lottery_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV_AREA\lottery_predictor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4706F3-0956-4399-A237-27AAA8454280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC8413-3D48-478B-8196-8F220B4EEA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1365" yWindow="330" windowWidth="22800" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,13 +244,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
